--- a/requirements/OntologyRequirements.xlsx
+++ b/requirements/OntologyRequirements.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="OntologyRequirementsTemplate (1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'OntologyRequirementsTemplate (1'!$A$1:$H$25</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'OntologyRequirementsTemplate (1'!$A$1:$H$27</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="78">
   <si>
     <t>Identifier</t>
   </si>
@@ -46,6 +46,9 @@
     <t>what is the name of the actor?</t>
   </si>
   <si>
+    <t>The value of the "name" attribute (String)</t>
+  </si>
+  <si>
     <t>Proposed</t>
   </si>
   <si>
@@ -55,6 +58,9 @@
     <t>What movies has the actor acted in ?</t>
   </si>
   <si>
+    <t>List of movie IDs from "movies_list" (Array of strings)</t>
+  </si>
+  <si>
     <t>List of movies where the actor participated</t>
   </si>
   <si>
@@ -64,6 +70,9 @@
     <t>what is the gender of the actor?</t>
   </si>
   <si>
+    <t>The value of the "gender" attribute (String)</t>
+  </si>
+  <si>
     <t>DirectorR1</t>
   </si>
   <si>
@@ -82,28 +91,40 @@
     <t>which movies has the director participated in?</t>
   </si>
   <si>
+    <t>List of "movie_id" where the person is "type": "director" inside "movies_list" array</t>
+  </si>
+  <si>
     <t>DirectorR4</t>
   </si>
   <si>
     <t>What is the first movie of the director?</t>
   </si>
   <si>
+    <t>The value of "first_movie" (Integer)</t>
+  </si>
+  <si>
     <t>DirectorR5</t>
   </si>
   <si>
     <t>What is the last movie of the director?</t>
   </si>
   <si>
+    <t>The value of "last_movie" (Integer)</t>
+  </si>
+  <si>
     <t>MovieR1</t>
   </si>
   <si>
     <t>What is the title of the movie?</t>
   </si>
   <si>
+    <t>The value of the "title" attribute (String)</t>
+  </si>
+  <si>
     <t>MovieR2</t>
   </si>
   <si>
-    <t xml:space="preserve">How much popular is the movie? </t>
+    <t xml:space="preserve">How popular is the movie? </t>
   </si>
   <si>
     <t>MovieR3</t>
@@ -136,24 +157,36 @@
     <t>What are the genres of the movie?</t>
   </si>
   <si>
+    <t>The values of the "genre" atrribute (Array of strings)</t>
+  </si>
+  <si>
     <t>MovieR9</t>
   </si>
   <si>
     <t>Who are the directors of the movie?</t>
   </si>
   <si>
+    <t xml:space="preserve">The value of the attribute "name" in the field "director" (String) </t>
+  </si>
+  <si>
     <t>MovieR10</t>
   </si>
   <si>
     <t>Who are the actos participated in the movie?</t>
   </si>
   <si>
+    <t>The values of the attribute "name" in the field of "all_actors" (Array of strings)</t>
+  </si>
+  <si>
     <t>MovieR11</t>
   </si>
   <si>
     <t>Date when the movie was released.</t>
   </si>
   <si>
+    <t>The value of the atrribute "year" (Integer)</t>
+  </si>
+  <si>
     <t>MovieR12</t>
   </si>
   <si>
@@ -166,19 +199,49 @@
     <t>Brief summary of the movie.</t>
   </si>
   <si>
+    <t>MovieR14</t>
+  </si>
+  <si>
+    <t>The percentage of female actors in the movie</t>
+  </si>
+  <si>
+    <t>The value of the "gender_percent" atrribute (Integer)</t>
+  </si>
+  <si>
+    <t>MovieR15</t>
+  </si>
+  <si>
+    <t>What was the budget of the movie?</t>
+  </si>
+  <si>
+    <t>The value of the "adjusted_budget" attribute (Integer)</t>
+  </si>
+  <si>
     <t>ProducerR1</t>
   </si>
   <si>
     <t>What is the first movie of the Producer?</t>
   </si>
   <si>
+    <t>The value of the "first_movie" attribute (Integer)</t>
+  </si>
+  <si>
     <t>ProducerR2</t>
   </si>
   <si>
+    <t>which movies has the producer participated in?</t>
+  </si>
+  <si>
+    <t>List of "movie_id" inside "movies_list" array</t>
+  </si>
+  <si>
     <t>ProducerR3</t>
   </si>
   <si>
     <t>What is the last movie of the Producer?</t>
+  </si>
+  <si>
+    <t>The value of the "last_movie" attribute (Integer)</t>
   </si>
   <si>
     <t>ProducerR4</t>
@@ -519,270 +582,349 @@
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="D2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>39</v>
+        <v>46</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>41</v>
+        <v>49</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>43</v>
+        <v>52</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>45</v>
+        <v>55</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>21</v>
+        <v>65</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>54</v>
+        <v>68</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>56</v>
+        <v>71</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$H$25">
-    <sortState ref="A1:H25">
-      <sortCondition ref="A1:A25"/>
+  <autoFilter ref="$A$1:$H$27">
+    <sortState ref="A1:H27">
+      <sortCondition ref="A1:A27"/>
     </sortState>
   </autoFilter>
   <drawing r:id="rId1"/>
